--- a/data/employees/EMP052/AST-EMP052-06.xlsx
+++ b/data/employees/EMP052/AST-EMP052-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Budget Tracker - Jordan Nguyen (Finance)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Jordan Nguyen | Role: Analyst | Location: Fremont | Date: 2025-03-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>89</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Cost Centre</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Budget ($K)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Actual ($K)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Variance ($K)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Variance %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>84</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CC-1001 Engineering</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2380</v>
-      </c>
-      <c r="D5" t="n">
-        <v>120</v>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>4.8</v>
+        <v>99</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Operational risk review. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CC-1002 Operations</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1920</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-120</v>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>-6.7</v>
+        <v>79</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Section 1: Fabric semantic model planning. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CC-1003 R&amp;D</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3200</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3100</v>
-      </c>
-      <c r="D7" t="n">
-        <v>100</v>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>3.1</v>
+        <v>65</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Operational risk review. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CC-1004 IT</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1195</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4</v>
+        <v>66</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>Section 1: Data quality remediation. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>63</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>76</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>72</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>70</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>77</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>85</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>76</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>62</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>72</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>95</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>85</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>84</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>81</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>85</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>93</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>89</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp052 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>84</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP052</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP052 contributes to ast emp052 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>